--- a/artfynd/A 23601-2025 artfynd.xlsx
+++ b/artfynd/A 23601-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,6 +1252,103 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126057390</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grössjöbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>550033</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6943282</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Borgsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23601-2025 artfynd.xlsx
+++ b/artfynd/A 23601-2025 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>126057390</v>
       </c>
       <c r="B7" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23601-2025 artfynd.xlsx
+++ b/artfynd/A 23601-2025 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>126057390</v>
       </c>
       <c r="B7" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23601-2025 artfynd.xlsx
+++ b/artfynd/A 23601-2025 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>126057390</v>
       </c>
       <c r="B7" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23601-2025 artfynd.xlsx
+++ b/artfynd/A 23601-2025 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>126057390</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
